--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/UTAH_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/UTAH_2021.xlsx
@@ -1399,7 +1399,7 @@
         <v>9</v>
       </c>
       <c r="D58">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="59">
@@ -1939,7 +1939,7 @@
         <v>9</v>
       </c>
       <c r="D88">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="89">
@@ -5028,7 +5028,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C260">
@@ -5190,7 +5190,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C269">
@@ -6223,7 +6223,7 @@
         <v>9</v>
       </c>
       <c r="D326">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="327">
@@ -6295,7 +6295,7 @@
         <v>9</v>
       </c>
       <c r="D330">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="331">
@@ -6331,7 +6331,7 @@
         <v>98</v>
       </c>
       <c r="D332">
-        <v>0.009869083585095671</v>
+        <v>0.009869083585095672</v>
       </c>
     </row>
     <row r="333">
@@ -7141,7 +7141,7 @@
         <v>9</v>
       </c>
       <c r="D377">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="378">
@@ -8923,7 +8923,7 @@
         <v>9</v>
       </c>
       <c r="D476">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="477">
@@ -9121,7 +9121,7 @@
         <v>9</v>
       </c>
       <c r="D487">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="488">
@@ -9157,7 +9157,7 @@
         <v>9</v>
       </c>
       <c r="D489">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="490">
@@ -10237,7 +10237,7 @@
         <v>9</v>
       </c>
       <c r="D549">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="550">
@@ -10741,7 +10741,7 @@
         <v>9</v>
       </c>
       <c r="D577">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="578">
@@ -10813,7 +10813,7 @@
         <v>9</v>
       </c>
       <c r="D581">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="582">
@@ -10993,7 +10993,7 @@
         <v>9</v>
       </c>
       <c r="D591">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="592">
@@ -12001,7 +12001,7 @@
         <v>9</v>
       </c>
       <c r="D647">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="648">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="B727" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C727">
@@ -15061,7 +15061,7 @@
         <v>9</v>
       </c>
       <c r="D817">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="818">
@@ -15097,7 +15097,7 @@
         <v>9</v>
       </c>
       <c r="D819">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="820">
@@ -15259,7 +15259,7 @@
         <v>9</v>
       </c>
       <c r="D828">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="829">
@@ -15727,7 +15727,7 @@
         <v>9</v>
       </c>
       <c r="D854">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="855">
@@ -15925,7 +15925,7 @@
         <v>9</v>
       </c>
       <c r="D865">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="866">
@@ -15943,7 +15943,7 @@
         <v>9</v>
       </c>
       <c r="D866">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="867">
@@ -17599,7 +17599,7 @@
         <v>9</v>
       </c>
       <c r="D958">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="959">
@@ -17869,7 +17869,7 @@
         <v>9</v>
       </c>
       <c r="D973">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="974">
@@ -18211,7 +18211,7 @@
         <v>9</v>
       </c>
       <c r="D992">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="993">
@@ -18463,7 +18463,7 @@
         <v>9</v>
       </c>
       <c r="D1006">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="1007">
@@ -19633,7 +19633,7 @@
         <v>9</v>
       </c>
       <c r="D1071">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="1072">
@@ -19957,7 +19957,7 @@
         <v>9</v>
       </c>
       <c r="D1089">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="1090">
@@ -20893,7 +20893,7 @@
         <v>9</v>
       </c>
       <c r="D1141">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="1142">
@@ -21271,7 +21271,7 @@
         <v>9</v>
       </c>
       <c r="D1162">
-        <v>0.0009063444108761329</v>
+        <v>0.0009063444108761328</v>
       </c>
     </row>
     <row r="1163">
